--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8698.530000000001</v>
+        <v>8608.610000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34153.84</v>
+        <v>33800.79</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>48598.71</v>
+        <v>48064.67</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31709.63</v>
+        <v>31938.36</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45946.04</v>
+        <v>44886.68</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>54069.98</v>
+        <v>54413.21</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>427192.07</v>
+        <v>430686.32</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>43875.18</v>
+        <v>43601.31</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20171.64</v>
+        <v>20088.06</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>43698.98</v>
+        <v>42439.6</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10503.61</v>
+        <v>10773.86</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25458.95</v>
+        <v>25657.49</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28223.23</v>
+        <v>28451.98</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37000.89</v>
+        <v>36778.34</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11167.41</v>
+        <v>11222.46</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32185.75</v>
+        <v>32429.11</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>450579.75</v>
+        <v>452162.74</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>33018.3</v>
+        <v>33134.3</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>48432.45</v>
+        <v>48676.54</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,68 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7209.65</v>
+        <v>7187.44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1607-76-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BINARY BAG</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.848.560-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>752030.39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1469-3470-CM25</t>
+          <t>1469-2770-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8608.610000000001</v>
+        <v>19842.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5401-5-CM25</t>
+          <t>1469-3470-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Maule</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>33800.79</v>
+        <v>8608.610000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1469-3580-CM25</t>
+          <t>5401-5-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>Servicio de Salud del Maule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DATCO CHILE S A</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.897.630-3</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>48064.67</v>
+        <v>33800.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3756-813-SE25</t>
+          <t>1469-3580-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,32 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>DATCO CHILE S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
+          <t>96.897.630-3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31938.36</v>
+        <v>48064.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5056-3839-CM25</t>
+          <t>3756-813-SE25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,28 +798,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44886.68</v>
+        <v>31938.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2436-59-CM26</t>
+          <t>5056-3839-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -838,22 +838,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>54413.21</v>
+        <v>44886.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3756-897-CM25</t>
+          <t>2436-59-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +894,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>430686.32</v>
+        <v>54413.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1469-528-CM26</t>
+          <t>3756-897-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>43601.31</v>
+        <v>430686.32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>872535-79-CM26</t>
+          <t>1469-528-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20088.06</v>
+        <v>43601.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3880-130-CM26</t>
+          <t>872535-79-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,27 +1077,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>42439.6</v>
+        <v>20088.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4473-151-CM26</t>
+          <t>3880-130-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10773.86</v>
+        <v>42439.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2291-780-CM26</t>
+          <t>4473-151-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25657.49</v>
+        <v>10773.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1469-1393-CM26</t>
+          <t>2291-780-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28451.98</v>
+        <v>25657.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2291-1022-CM26</t>
+          <t>1469-1393-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>36778.34</v>
+        <v>28451.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5056-2151-CM26</t>
+          <t>2291-1022-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11222.46</v>
+        <v>36778.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2320-223-CM26</t>
+          <t>5056-2151-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32429.11</v>
+        <v>11222.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4134-401-CM26</t>
+          <t>2320-223-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>452162.74</v>
+        <v>32429.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1469-1843-CM26</t>
+          <t>4134-401-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>33134.3</v>
+        <v>452162.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1233619-860-CM26</t>
+          <t>1469-1843-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>48676.54</v>
+        <v>33134.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4343-131-CM26</t>
+          <t>1233619-860-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,22 +1692,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>ANDESTIC SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7187.44</v>
+        <v>48676.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1607-76-CM26</t>
+          <t>4343-131-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1748,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BINARY BAG</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.848.560-7</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,6 +1793,67 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
+        <v>7187.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1607-76-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BINARY BAG</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.848.560-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>752030.39</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1469-2770-CM25</t>
+          <t>3756-429-CM24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>19842.27</v>
+        <v>313544.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1469-3470-CM25</t>
+          <t>1469-573-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8608.610000000001</v>
+        <v>21196.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5401-5-CM25</t>
+          <t>872535-67-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Maule</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>33800.79</v>
+        <v>21737.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1469-3580-CM25</t>
+          <t>1469-796-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DATCO CHILE S A</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.897.630-3</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>48064.67</v>
+        <v>13304.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3756-813-SE25</t>
+          <t>2291-852-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,32 +798,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31938.36</v>
+        <v>45683.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5056-3839-CM25</t>
+          <t>1469-1704-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44886.68</v>
+        <v>41437.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2436-59-CM26</t>
+          <t>1469-2264-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -909,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>54413.21</v>
+        <v>22060.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3756-897-CM25</t>
+          <t>1469-2341-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SERVICIOS Y CONSULTORIAS EN INFORMATICA CLIOBYTE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>77.479.175-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>430686.32</v>
+        <v>24048.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1469-528-CM26</t>
+          <t>1469-2770-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>43601.31</v>
+        <v>19842.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>872535-79-CM26</t>
+          <t>1233619-1034-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20088.06</v>
+        <v>13639.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3880-130-CM26</t>
+          <t>2298-5153-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>42439.6</v>
+        <v>51564.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4473-151-CM26</t>
+          <t>1469-3470-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10773.86</v>
+        <v>8608.610000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2291-780-CM26</t>
+          <t>5401-5-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Servicio de Salud del Maule</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>25657.49</v>
+        <v>33800.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1469-1393-CM26</t>
+          <t>1469-3580-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1351,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>DATCO CHILE S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.897.630-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>28451.98</v>
+        <v>48064.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2291-1022-CM26</t>
+          <t>3756-813-SE25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,28 +1408,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>36778.34</v>
+        <v>31938.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5056-2151-CM26</t>
+          <t>5056-3839-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11222.46</v>
+        <v>44886.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2320-223-CM26</t>
+          <t>2436-59-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>32429.11</v>
+        <v>54413.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4134-401-CM26</t>
+          <t>3756-897-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,27 +1565,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>452162.74</v>
+        <v>430686.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1469-1843-CM26</t>
+          <t>1469-528-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>33134.3</v>
+        <v>43601.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1233619-860-CM26</t>
+          <t>872535-79-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>48676.54</v>
+        <v>20088.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4343-131-CM26</t>
+          <t>3880-130-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1748,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7187.44</v>
+        <v>42439.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1607-76-CM26</t>
+          <t>4473-151-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,27 +1809,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BINARY BAG</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.848.560-7</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,7 +1854,861 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
+        <v>10773.86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2291-780-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>25657.49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1469-1393-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>28451.98</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2291-1022-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>36778.34</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5056-2151-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.606.901-2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ZECOVERY LTDA   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>11222.46</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2320-223-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>GEORG</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>32429.11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4134-401-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>452162.74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1469-1843-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Seidor Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.986.170-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>33134.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1233619-860-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.980.930-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ANDESTIC SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.031.392-0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>48676.54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4343-131-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.606.912-8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>GEORG</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>7187.44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1607-76-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BINARY BAG</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.848.560-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>752030.39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1469-2275-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>59382.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4452-736-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>INFO WORLD SA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.532.020-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>24725.55</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1469-2464-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>FabricApp SpA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.650.494-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>40142.28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4168-1247-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>36252.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Maule</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2165,7 +2165,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4134-401-CM26</t>
+          <t>1469-1843-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>452162.74</v>
+        <v>33134.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1469-1843-CM26</t>
+          <t>4134-401-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>33134.3</v>
+        <v>452162.74</v>
       </c>
     </row>
     <row r="31">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2709,6 +2709,128 @@
       </c>
       <c r="M37" s="2" t="n">
         <v>36252.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1469-2066-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>301884.06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1469-2745-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>23046.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -562,7 +562,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.479.175-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1513,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1578,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1643,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1708,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1895,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2021,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2147,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2212,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2277,11 @@
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2342,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2468,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2594,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2781,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2846,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2911,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2229,7 +2229,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1469-1843-CM26</t>
+          <t>4134-401-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>33134.3</v>
+        <v>452162.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4134-401-CM26</t>
+          <t>1469-1843-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>452162.74</v>
+        <v>33134.3</v>
       </c>
     </row>
     <row r="31">
@@ -2672,7 +2672,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1469-2464-CM26</t>
+          <t>4168-1247-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2712,28 +2712,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FabricApp SpA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.650.494-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>40142.28</v>
+        <v>36252.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4168-1247-CM26</t>
+          <t>1469-2464-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2758,12 +2762,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2773,26 +2777,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>FabricApp SpA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.650.494-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>36252.2</v>
+        <v>40142.28</v>
       </c>
     </row>
     <row r="38">
@@ -2923,6 +2923,193 @@
       </c>
       <c r="M39" s="2" t="n">
         <v>23046.81</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1469-2995-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>20090.88</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1233619-1252-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.980.930-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.046.871-1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>13933.04</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4452-737-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>INFO WORLD SA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>96.532.020-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>70387.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/maule.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
